--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104511_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104511_W6.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.842</v>
+        <v>11.1178</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6169</v>
+        <v>7.645</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2251</v>
+        <v>3.4728</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1746</v>
+        <v>6.154</v>
       </c>
       <c r="H2" t="n">
-        <v>1.462</v>
+        <v>1.4456</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7126</v>
+        <v>4.7085</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3045</v>
+        <v>6.2667</v>
       </c>
       <c r="K2" t="n">
-        <v>1.416</v>
+        <v>1.3887</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8885</v>
+        <v>4.878</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1299</v>
+        <v>-0.1127</v>
       </c>
       <c r="N2" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1473</v>
+        <v>0.1427</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3266</v>
+        <v>-0.2559</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1793</v>
+        <v>0.3986</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0271</v>
+        <v>7.1537</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3299</v>
+        <v>3.5836</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6971</v>
+        <v>3.5701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8929</v>
+        <v>0.865</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I3" t="n">
-        <v>1.082</v>
+        <v>1.0518</v>
       </c>
       <c r="J3" t="n">
-        <v>1.38</v>
+        <v>1.3356</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4737</v>
+        <v>1.4358</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4871</v>
+        <v>-0.4706</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3856</v>
+        <v>0.5375</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3962</v>
+        <v>-0.0887</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.6262</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7343</v>
+        <v>5.2085</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3929</v>
+        <v>4.4871</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3414</v>
+        <v>0.7214</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2103</v>
+        <v>7.1936</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6262</v>
+        <v>-0.6261</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8365</v>
+        <v>7.8197</v>
       </c>
       <c r="J4" t="n">
-        <v>7.6169</v>
+        <v>7.5813</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1936</v>
+        <v>0.1789</v>
       </c>
       <c r="L4" t="n">
-        <v>7.4233</v>
+        <v>7.4025</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4066</v>
+        <v>-0.3877</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.198</v>
+        <v>-0.7166</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9557</v>
+        <v>-0.8179</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2423</v>
+        <v>0.1013</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6633</v>
+        <v>4.3862</v>
       </c>
       <c r="E5" t="n">
-        <v>0.977</v>
+        <v>1.5659</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6863</v>
+        <v>2.8203</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8458</v>
+        <v>1.8474</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6277</v>
+        <v>0.6289</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2181</v>
+        <v>1.2185</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9806</v>
+        <v>1.9614</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2743</v>
+        <v>1.2615</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7063</v>
+        <v>0.6998</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1348</v>
+        <v>-0.1139</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.878</v>
+        <v>-0.1732</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1644</v>
+        <v>-0.5532</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2864</v>
+        <v>0.3801</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0606</v>
+        <v>3.483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7463</v>
+        <v>1.3895</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3143</v>
+        <v>2.0935</v>
       </c>
       <c r="G6" t="n">
         <v>0.8447</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1703</v>
+        <v>0.1668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6744</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1719</v>
+        <v>1.1602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3272</v>
+        <v>-0.3155</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0278</v>
+        <v>0.3831</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.747</v>
+        <v>-0.0863</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7192</v>
+        <v>0.4694</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8395</v>
+        <v>2.1385</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8456</v>
+        <v>0.1918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9939</v>
+        <v>1.9467</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7065</v>
+        <v>-1.5663</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0028</v>
+        <v>-1.3352</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7037</v>
+        <v>-0.2311</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7778</v>
+        <v>-0.6627</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9568</v>
+        <v>-0.3867</v>
       </c>
       <c r="L7" t="n">
-        <v>0.821</v>
+        <v>-0.276</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0712</v>
+        <v>-0.9036</v>
       </c>
       <c r="N7" t="n">
-        <v>0.046</v>
+        <v>-0.9485</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>0.0449</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>2.7316</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9061</v>
+        <v>-0.1163</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9467</v>
+        <v>-0.2349</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0405</v>
+        <v>0.1187</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6105</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7819</v>
+        <v>1.0964</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2009</v>
+        <v>-0.0514</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9829</v>
+        <v>1.1478</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5555</v>
+        <v>2.7108</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3289</v>
+        <v>2.0046</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2266</v>
+        <v>0.7062</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6343</v>
+        <v>2.767</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3676</v>
+        <v>1.9478</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2666</v>
+        <v>0.8192</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9212</v>
+        <v>-0.0562</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9612000000000001</v>
+        <v>0.0568</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>2.722</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4773</v>
+        <v>0.1579</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6593</v>
+        <v>0.0741</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1821</v>
+        <v>0.0838</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>-0.6162</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.7509</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8614000000000001</v>
+        <v>-1.0619</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2489</v>
+        <v>1.8128</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4244</v>
+        <v>-2.0817</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.443</v>
+        <v>-0.7785</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0186</v>
+        <v>-1.3033</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2276</v>
+        <v>-1.3242</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5208</v>
+        <v>-0.7207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2931</v>
+        <v>-0.6035</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1967</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2745</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1956</v>
+        <v>0.8327</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8771</v>
+        <v>0.311</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3185</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2541</v>
+        <v>-0.1128</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7576</v>
+        <v>-0.8318</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0117</v>
+        <v>0.719</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0868</v>
+        <v>-0.8082</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.3359</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3061</v>
+        <v>-1.144</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3169</v>
+        <v>-0.1636</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7171</v>
+        <v>0.5516</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5998</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7699</v>
+        <v>-0.6446</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0636</v>
+        <v>-0.2157</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7063</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3408</v>
+        <v>-0.0558</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7401</v>
+        <v>0.2254</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.3121</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6276</v>
+        <v>0.0067</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5401</v>
+        <v>-0.3188</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2835</v>
+        <v>-1.4302</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4487</v>
+        <v>-1.4418</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7321</v>
+        <v>0.0116</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2238</v>
+        <v>-1.245</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7242</v>
+        <v>-1.5276</v>
       </c>
       <c r="L11" t="n">
-        <v>2.948</v>
+        <v>0.2826</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9404</v>
+        <v>-0.1852</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7245</v>
+        <v>0.0857</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2159</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1067</v>
+        <v>0.2775</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2431</v>
+        <v>0.0531</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>0.2243</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.6636</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>2.3367</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8243</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0478</v>
+        <v>-0.7009</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9424</v>
+        <v>2.785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8946</v>
+        <v>-3.4858</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8102</v>
+        <v>1.2742</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3333</v>
+        <v>-1.453</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1435</v>
+        <v>2.7273</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1576</v>
+        <v>2.207</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5541</v>
+        <v>-0.7347</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7117</v>
+        <v>2.9417</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6526</v>
+        <v>-0.9328</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2209</v>
+        <v>-0.7184</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4318</v>
+        <v>-0.2144</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0139</v>
+        <v>0.3145</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3992</v>
+        <v>0.4202</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4131</v>
+        <v>-0.1057</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3856</v>
+        <v>-3.6554</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1743</v>
+        <v>-1.8263</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.275</v>
+        <v>-4.1075</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1006</v>
+        <v>2.2812</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6345</v>
+        <v>-1.63</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3523</v>
+        <v>-0.3396</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2822</v>
+        <v>-1.2904</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4169</v>
+        <v>-1.4291</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5381</v>
+        <v>-1.5497</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2176</v>
+        <v>-0.2009</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7667</v>
+        <v>-0.4239</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5898</v>
+        <v>-0.4021</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1769</v>
+        <v>-0.0218</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.6806</v>
+        <v>32.3829</v>
       </c>
       <c r="E14" t="n">
-        <v>15.2217</v>
+        <v>15.602</v>
       </c>
       <c r="F14" t="n">
-        <v>16.4589</v>
+        <v>16.781</v>
       </c>
       <c r="G14" t="n">
-        <v>13.4469</v>
+        <v>13.3733</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5728</v>
+        <v>-1.5792</v>
       </c>
       <c r="I14" t="n">
-        <v>15.0196</v>
+        <v>14.9527</v>
       </c>
       <c r="J14" t="n">
-        <v>18.7022</v>
+        <v>18.4546</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0033</v>
+        <v>2.8789</v>
       </c>
       <c r="L14" t="n">
-        <v>15.6989</v>
+        <v>15.5759</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.2552</v>
+        <v>-5.081300000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.576199999999999</v>
+        <v>-4.4584</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6793</v>
+        <v>-0.6231</v>
       </c>
       <c r="P14" t="n">
-        <v>20.415</v>
+        <v>20.4868</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R14" t="n">
-        <v>29.4885</v>
+        <v>29.5921</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4535999999999999</v>
+        <v>1.1601</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5705</v>
+        <v>-1.8618</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0244</v>
+        <v>3.022</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6351</v>
+        <v>-2.6373</v>
       </c>
       <c r="W14" t="n">
-        <v>8.163300000000001</v>
+        <v>8.1145</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.7983</v>
+        <v>-10.7518</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SORIANO</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3505</v>
+        <v>0.3057</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3059</v>
+        <v>2.5996</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9554</v>
+        <v>-2.2939</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1169</v>
+        <v>-2.8211</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8715000000000001</v>
+        <v>1.7693</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9884</v>
+        <v>-4.5904</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2997</v>
+        <v>0.3688</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1878</v>
+        <v>1.7991</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>-1.4303</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4166</v>
+        <v>-3.1899</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.0298</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1003</v>
+        <v>-3.1601</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2594</v>
+        <v>-0.21</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3822</v>
+        <v>-0.602</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1228</v>
+        <v>0.392</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2495</v>
+        <v>2.8814</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8924</v>
+        <v>3.9709</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6429</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2483</v>
+        <v>-0.0859</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2642</v>
+        <v>0.8616</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0159</v>
+        <v>-0.9475</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6491</v>
+        <v>1.6543</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8889</v>
+        <v>1.8816</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2398</v>
+        <v>-0.2274</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9879</v>
+        <v>3.9587</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7565</v>
+        <v>2.7299</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3388</v>
+        <v>-2.3045</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4712</v>
+        <v>-1.4562</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3853</v>
+        <v>0.0629</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1966</v>
+        <v>-0.156</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1887</v>
+        <v>0.2189</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>J. SORIANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1104</v>
+        <v>-0.2393</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2931</v>
+        <v>2.3333</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4035</v>
+        <v>-2.5726</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8313</v>
+        <v>-1.1031</v>
       </c>
       <c r="H17" t="n">
-        <v>1.772</v>
+        <v>0.873</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.6033</v>
+        <v>-1.9762</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3979</v>
+        <v>1.2871</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8214</v>
+        <v>1.1754</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4234</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2292</v>
+        <v>-2.3902</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0494</v>
+        <v>-0.3023</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1798</v>
+        <v>-2.0879</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6252</v>
+        <v>0.6622</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9557</v>
+        <v>0.4411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3305</v>
+        <v>0.2211</v>
       </c>
       <c r="V17" t="n">
-        <v>2.8924</v>
+        <v>2.2504</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9851</v>
+        <v>2.8814</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6712</v>
+        <v>-0.3478</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7071</v>
+        <v>0.8179</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3783</v>
+        <v>-1.1657</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2669</v>
+        <v>0.2718</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0057</v>
+        <v>0.0112</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0368</v>
+        <v>1.0294</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7699</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3632</v>
+        <v>-0.0569</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0336</v>
+        <v>0.1546</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1591</v>
+        <v>-1.0449</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1293</v>
+        <v>-0.9214</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0298</v>
+        <v>-0.1235</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0331</v>
+        <v>-0.0183</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2783</v>
+        <v>1.2863</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3114</v>
+        <v>-1.3046</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0168</v>
+        <v>0.0045</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0498</v>
+        <v>-0.0229</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1469</v>
+        <v>1.1623</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4721</v>
+        <v>-0.3633</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6775</v>
+        <v>-0.4416</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2053</v>
+        <v>0.0784</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8268</v>
+        <v>-1.547</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5577</v>
+        <v>-1.4537</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.269</v>
+        <v>-0.0934</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0276</v>
+        <v>0.0345</v>
       </c>
       <c r="H20" t="n">
-        <v>1.443</v>
+        <v>1.4418</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4153</v>
+        <v>-1.4073</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1975</v>
+        <v>1.1921</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1699</v>
+        <v>-1.1576</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1059</v>
+        <v>0.1696</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3811</v>
+        <v>0.5391</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.556</v>
+        <v>-5.9703</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5488</v>
+        <v>-3.4619</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0072</v>
+        <v>-2.5084</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7841</v>
+        <v>-1.779</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3332</v>
+        <v>-2.3349</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5492</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2248</v>
+        <v>0.2128</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0089</v>
+        <v>-1.9918</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2087</v>
+        <v>0.3809</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U21" t="n">
-        <v>0.121</v>
+        <v>0.5925</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>E. STEVENSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0915</v>
+        <v>-6.5954</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.792</v>
+        <v>-3.8167</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2996</v>
+        <v>-2.7787</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4568</v>
+        <v>-4.5467</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2311</v>
+        <v>-1.6911</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2257</v>
+        <v>-2.8556</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0743</v>
+        <v>-1.7132</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4156</v>
+        <v>-0.9005</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3413</v>
+        <v>-0.8126</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5311</v>
+        <v>-2.8335</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.7906</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8844</v>
+        <v>-2.043</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.8562</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6179</v>
+        <v>0.7237</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3297</v>
+        <v>-0.3719</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2882</v>
+        <v>1.0956</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. STEVENSON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1059</v>
+        <v>-6.6828</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0013</v>
+        <v>-4.8194</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1046</v>
+        <v>-1.8634</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.5357</v>
+        <v>-2.4429</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6809</v>
+        <v>-0.2189</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8548</v>
+        <v>-2.2239</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6714</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8769</v>
+        <v>0.4137</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7945</v>
+        <v>-0.3505</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8643</v>
+        <v>-2.5061</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0603</v>
+        <v>-1.8734</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2029</v>
+        <v>-0.2124</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>-0.33</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8108</v>
+        <v>0.1176</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7585</v>
+        <v>-7.8991</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.0002</v>
+        <v>-8.920299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2417</v>
+        <v>1.0213</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.633</v>
+        <v>-2.623</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4416</v>
+        <v>-1.439</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1914</v>
+        <v>-1.1839</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3091</v>
+        <v>-1.3222</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3239</v>
+        <v>-1.3007</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.2172</v>
+        <v>-5.2355</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0916</v>
+        <v>-0.0406</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>-0.7692</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9778</v>
+        <v>0.7286</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.6806</v>
+        <v>-30.1068</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.459</v>
+        <v>-16.781</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.2216</v>
+        <v>-13.3258</v>
       </c>
       <c r="G25" t="n">
-        <v>-13.4473</v>
+        <v>-13.3735</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5726</v>
+        <v>1.5793</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.0197</v>
+        <v>-14.9527</v>
       </c>
       <c r="J25" t="n">
-        <v>5.255199999999998</v>
+        <v>5.081200000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5762</v>
+        <v>4.4582</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6792000000000001</v>
+        <v>0.6231000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.7024</v>
+        <v>-18.4548</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.003200000000001</v>
+        <v>-2.8789</v>
       </c>
       <c r="O25" t="n">
-        <v>-15.6988</v>
+        <v>-15.5759</v>
       </c>
       <c r="P25" t="n">
-        <v>-20.415</v>
+        <v>-20.4867</v>
       </c>
       <c r="Q25" t="n">
-        <v>-29.4883</v>
+        <v>-29.592</v>
       </c>
       <c r="R25" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4538</v>
+        <v>1.1161</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0244</v>
+        <v>-3.0221</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5706</v>
+        <v>4.1384</v>
       </c>
       <c r="V25" t="n">
-        <v>2.6352</v>
+        <v>2.637300000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>10.7984</v>
+        <v>10.7518</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.1632</v>
+        <v>-8.114600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104511_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104511_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.7518</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104511_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.114600000000001</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
